--- a/human_resources_forms/021_hr_professional_certification_registration_form--human_resources_forms.xlsx
+++ b/human_resources_forms/021_hr_professional_certification_registration_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -988,12 +988,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Select One 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Interests</t>
+          <t>Select Multiple 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1113,7 +1113,7 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1240,58 +1240,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1342,58 +1342,58 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1410,7 +1410,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1444,58 +1444,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
